--- a/audit-schedule/Audit_Schedule_JuLY_2026_TRANSGUARD_DM.xlsx
+++ b/audit-schedule/Audit_Schedule_JuLY_2026_TRANSGUARD_DM.xlsx
@@ -741,7 +741,7 @@
     <xf numFmtId="0" fontId="11" fillId="33" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="34" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -927,6 +927,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -6657,11 +6660,7 @@
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>
       <c r="F5" s="31" t="n"/>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="G5" s="31" t="n"/>
       <c r="H5" s="31" t="n"/>
       <c r="I5" s="31" t="n"/>
       <c r="J5" s="31" t="n"/>
@@ -6674,7 +6673,11 @@
       <c r="Q5" s="30" t="n"/>
       <c r="R5" s="32" t="n"/>
       <c r="S5" s="31" t="n"/>
-      <c r="T5" s="31" t="n"/>
+      <c r="T5" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="U5" s="31" t="n"/>
       <c r="V5" s="32" t="n"/>
       <c r="W5" s="31" t="n"/>
@@ -6708,11 +6711,7 @@
           <t>Inam/Fatima</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="C6" s="32" t="n"/>
       <c r="D6" s="31" t="n"/>
       <c r="E6" s="31" t="n"/>
       <c r="F6" s="31" t="n"/>
@@ -6724,7 +6723,11 @@
       <c r="L6" s="30" t="n"/>
       <c r="M6" s="30" t="n"/>
       <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
+      <c r="O6" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="P6" s="30" t="n"/>
       <c r="Q6" s="30" t="n"/>
       <c r="R6" s="31" t="n"/>
@@ -6765,14 +6768,14 @@
       </c>
       <c r="C7" s="32" t="n"/>
       <c r="D7" s="31" t="n"/>
-      <c r="E7" s="32" t="n"/>
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="F7" s="31" t="n"/>
       <c r="G7" s="31" t="n"/>
-      <c r="H7" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="H7" s="31" t="n"/>
       <c r="I7" s="32" t="n"/>
       <c r="J7" s="31" t="n"/>
       <c r="K7" s="31" t="n"/>
@@ -6819,7 +6822,11 @@
         </is>
       </c>
       <c r="C8" s="32" t="n"/>
-      <c r="D8" s="31" t="n"/>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="E8" s="32" t="n"/>
       <c r="F8" s="31" t="n"/>
       <c r="G8" s="31" t="n"/>
@@ -6828,11 +6835,7 @@
       <c r="J8" s="31" t="n"/>
       <c r="K8" s="31" t="n"/>
       <c r="L8" s="31" t="n"/>
-      <c r="M8" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="M8" s="31" t="n"/>
       <c r="N8" s="31" t="n"/>
       <c r="O8" s="31" t="n"/>
       <c r="P8" s="30" t="n"/>
@@ -6876,12 +6879,12 @@
       </c>
       <c r="C9" s="31" t="n"/>
       <c r="D9" s="30" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="n"/>
       <c r="G9" s="31" t="n"/>
       <c r="H9" s="31" t="n"/>
       <c r="I9" s="30" t="n"/>
@@ -6931,17 +6934,17 @@
         </is>
       </c>
       <c r="C10" s="31" t="n"/>
-      <c r="D10" s="32" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="D10" s="32" t="n"/>
       <c r="E10" s="32" t="n"/>
       <c r="F10" s="30" t="n"/>
       <c r="G10" s="31" t="n"/>
       <c r="H10" s="31" t="n"/>
       <c r="I10" s="31" t="n"/>
-      <c r="J10" s="32" t="n"/>
+      <c r="J10" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="K10" s="32" t="n"/>
       <c r="L10" s="31" t="n"/>
       <c r="M10" s="31" t="n"/>
@@ -6995,14 +6998,14 @@
       <c r="I11" s="31" t="n"/>
       <c r="J11" s="31" t="n"/>
       <c r="K11" s="31" t="n"/>
-      <c r="L11" s="32" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="L11" s="32" t="n"/>
       <c r="M11" s="31" t="n"/>
       <c r="N11" s="31" t="n"/>
-      <c r="O11" s="31" t="n"/>
+      <c r="O11" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="P11" s="30" t="n"/>
       <c r="Q11" s="30" t="n"/>
       <c r="R11" s="30" t="n"/>
@@ -7047,12 +7050,12 @@
       <c r="E12" s="31" t="n"/>
       <c r="F12" s="30" t="n"/>
       <c r="G12" s="31" t="n"/>
-      <c r="H12" s="30" t="n"/>
-      <c r="I12" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="H12" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I12" s="31" t="n"/>
       <c r="J12" s="31" t="n"/>
       <c r="K12" s="31" t="n"/>
       <c r="L12" s="32" t="n"/>
@@ -7101,11 +7104,7 @@
       <c r="C13" s="31" t="n"/>
       <c r="D13" s="31" t="n"/>
       <c r="E13" s="31" t="n"/>
-      <c r="F13" s="30" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="F13" s="30" t="n"/>
       <c r="G13" s="33" t="n"/>
       <c r="H13" s="31" t="n"/>
       <c r="I13" s="30" t="n"/>
@@ -7121,7 +7120,11 @@
       <c r="S13" s="31" t="n"/>
       <c r="T13" s="31" t="n"/>
       <c r="U13" s="31" t="n"/>
-      <c r="V13" s="31" t="n"/>
+      <c r="V13" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="W13" s="31" t="n"/>
       <c r="X13" s="33" t="n"/>
       <c r="Y13" s="31" t="n"/>
@@ -7166,18 +7169,18 @@
       <c r="M14" s="32" t="n"/>
       <c r="N14" s="31" t="n"/>
       <c r="O14" s="31" t="n"/>
-      <c r="P14" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="P14" s="31" t="n"/>
       <c r="Q14" s="31" t="n"/>
       <c r="R14" s="31" t="n"/>
       <c r="S14" s="31" t="n"/>
       <c r="T14" s="31" t="n"/>
       <c r="U14" s="31" t="n"/>
       <c r="V14" s="31" t="n"/>
-      <c r="W14" s="31" t="n"/>
+      <c r="W14" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="X14" s="31" t="n"/>
       <c r="Y14" s="32" t="n"/>
       <c r="Z14" s="31" t="n"/>
@@ -7215,17 +7218,17 @@
       <c r="F15" s="31" t="n"/>
       <c r="G15" s="30" t="n"/>
       <c r="H15" s="31" t="n"/>
-      <c r="I15" s="31" t="n"/>
+      <c r="I15" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="J15" s="31" t="n"/>
       <c r="K15" s="31" t="n"/>
       <c r="L15" s="30" t="n"/>
       <c r="M15" s="32" t="n"/>
       <c r="N15" s="30" t="n"/>
-      <c r="O15" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="O15" s="31" t="n"/>
       <c r="P15" s="31" t="n"/>
       <c r="Q15" s="31" t="n"/>
       <c r="R15" s="31" t="n"/>
@@ -7269,11 +7272,7 @@
       <c r="D16" s="30" t="n"/>
       <c r="E16" s="31" t="n"/>
       <c r="F16" s="31" t="n"/>
-      <c r="G16" s="30" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="G16" s="30" t="n"/>
       <c r="H16" s="31" t="n"/>
       <c r="I16" s="31" t="n"/>
       <c r="J16" s="31" t="n"/>
@@ -7283,7 +7282,11 @@
       <c r="N16" s="30" t="n"/>
       <c r="O16" s="30" t="n"/>
       <c r="P16" s="31" t="n"/>
-      <c r="Q16" s="31" t="n"/>
+      <c r="Q16" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="R16" s="36" t="n"/>
       <c r="S16" s="31" t="n"/>
       <c r="T16" s="31" t="n"/>
@@ -7337,15 +7340,15 @@
       <c r="P17" s="31" t="n"/>
       <c r="Q17" s="31" t="n"/>
       <c r="R17" s="36" t="n"/>
-      <c r="S17" s="30" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="S17" s="30" t="n"/>
       <c r="T17" s="31" t="n"/>
       <c r="U17" s="32" t="n"/>
       <c r="V17" s="32" t="n"/>
-      <c r="W17" s="32" t="n"/>
+      <c r="W17" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="X17" s="32" t="n"/>
       <c r="Y17" s="31" t="n"/>
       <c r="Z17" s="31" t="n"/>
@@ -7379,17 +7382,17 @@
       </c>
       <c r="C18" s="31" t="n"/>
       <c r="D18" s="31" t="n"/>
-      <c r="E18" s="30" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="E18" s="30" t="n"/>
       <c r="F18" s="31" t="n"/>
       <c r="G18" s="30" t="n"/>
       <c r="H18" s="31" t="n"/>
       <c r="I18" s="31" t="n"/>
       <c r="J18" s="31" t="n"/>
-      <c r="K18" s="31" t="n"/>
+      <c r="K18" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="L18" s="31" t="n"/>
       <c r="M18" s="31" t="n"/>
       <c r="N18" s="31" t="n"/>
@@ -7443,14 +7446,14 @@
       <c r="J19" s="31" t="n"/>
       <c r="K19" s="30" t="n"/>
       <c r="L19" s="31" t="n"/>
-      <c r="M19" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="M19" s="31" t="n"/>
       <c r="N19" s="31" t="n"/>
       <c r="O19" s="31" t="n"/>
-      <c r="P19" s="31" t="n"/>
+      <c r="P19" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="Q19" s="31" t="n"/>
       <c r="R19" s="30" t="n"/>
       <c r="S19" s="31" t="n"/>
@@ -7508,14 +7511,14 @@
       <c r="S20" s="32" t="n"/>
       <c r="T20" s="31" t="n"/>
       <c r="U20" s="31" t="n"/>
-      <c r="V20" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="V20" s="31" t="n"/>
       <c r="W20" s="32" t="n"/>
       <c r="X20" s="31" t="n"/>
-      <c r="Y20" s="31" t="n"/>
+      <c r="Y20" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="Z20" s="31" t="n"/>
       <c r="AA20" s="31" t="n"/>
       <c r="AB20" s="31" t="n"/>
@@ -7554,17 +7557,17 @@
       <c r="I21" s="31" t="n"/>
       <c r="J21" s="30" t="n"/>
       <c r="K21" s="31" t="n"/>
-      <c r="L21" s="31" t="n"/>
+      <c r="L21" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="M21" s="32" t="n"/>
       <c r="N21" s="31" t="n"/>
       <c r="O21" s="31" t="n"/>
       <c r="P21" s="31" t="n"/>
       <c r="Q21" s="31" t="n"/>
-      <c r="R21" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="R21" s="31" t="n"/>
       <c r="S21" s="31" t="n"/>
       <c r="T21" s="31" t="n"/>
       <c r="U21" s="31" t="n"/>
@@ -7612,11 +7615,7 @@
       <c r="L22" s="31" t="n"/>
       <c r="M22" s="32" t="n"/>
       <c r="N22" s="31" t="n"/>
-      <c r="O22" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="O22" s="31" t="n"/>
       <c r="P22" s="31" t="n"/>
       <c r="Q22" s="31" t="n"/>
       <c r="R22" s="31" t="n"/>
@@ -7633,7 +7632,11 @@
       <c r="AC22" s="31" t="n"/>
       <c r="AD22" s="31" t="n"/>
       <c r="AE22" s="33" t="n"/>
-      <c r="AF22" s="33" t="n"/>
+      <c r="AF22" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AG22" s="31" t="n"/>
       <c r="AH22" s="34" t="n"/>
       <c r="AI22" s="34">
@@ -7662,11 +7665,7 @@
       <c r="F23" s="32" t="n"/>
       <c r="G23" s="31" t="n"/>
       <c r="H23" s="30" t="n"/>
-      <c r="I23" s="30" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="I23" s="30" t="n"/>
       <c r="J23" s="31" t="n"/>
       <c r="K23" s="31" t="n"/>
       <c r="L23" s="31" t="n"/>
@@ -7675,7 +7674,11 @@
       <c r="O23" s="31" t="n"/>
       <c r="P23" s="30" t="n"/>
       <c r="Q23" s="30" t="n"/>
-      <c r="R23" s="30" t="n"/>
+      <c r="R23" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="S23" s="32" t="n"/>
       <c r="T23" s="32" t="n"/>
       <c r="U23" s="31" t="n"/>
@@ -7722,10 +7725,14 @@
       <c r="J24" s="31" t="n"/>
       <c r="K24" s="31" t="n"/>
       <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
+      <c r="M24" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="N24" s="31" t="n"/>
       <c r="O24" s="31" t="n"/>
-      <c r="P24" s="30" t="n"/>
+      <c r="P24" s="32" t="n"/>
       <c r="Q24" s="30" t="n"/>
       <c r="R24" s="31" t="n"/>
       <c r="S24" s="32" t="n"/>
@@ -7734,11 +7741,7 @@
       <c r="V24" s="31" t="n"/>
       <c r="W24" s="32" t="n"/>
       <c r="X24" s="31" t="n"/>
-      <c r="Y24" s="33" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="Y24" s="33" t="n"/>
       <c r="Z24" s="32" t="n"/>
       <c r="AA24" s="31" t="n"/>
       <c r="AB24" s="31" t="n"/>
@@ -7773,17 +7776,17 @@
       <c r="E25" s="31" t="n"/>
       <c r="F25" s="31" t="n"/>
       <c r="G25" s="31" t="n"/>
-      <c r="H25" s="31" t="n"/>
+      <c r="H25" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="I25" s="31" t="n"/>
       <c r="J25" s="31" t="n"/>
       <c r="K25" s="31" t="n"/>
       <c r="L25" s="31" t="n"/>
       <c r="M25" s="31" t="n"/>
-      <c r="N25" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="N25" s="31" t="n"/>
       <c r="O25" s="31" t="n"/>
       <c r="P25" s="31" t="n"/>
       <c r="Q25" s="31" t="n"/>
@@ -7827,11 +7830,7 @@
       <c r="C26" s="31" t="n"/>
       <c r="D26" s="31" t="n"/>
       <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="F26" s="31" t="n"/>
       <c r="G26" s="31" t="n"/>
       <c r="H26" s="31" t="n"/>
       <c r="I26" s="31" t="n"/>
@@ -7848,14 +7847,14 @@
       <c r="T26" s="32" t="n"/>
       <c r="U26" s="30" t="n"/>
       <c r="V26" s="30" t="n"/>
-      <c r="W26" s="32" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="W26" s="32" t="n"/>
       <c r="X26" s="30" t="n"/>
       <c r="Y26" s="31" t="n"/>
-      <c r="Z26" s="31" t="n"/>
+      <c r="Z26" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AA26" s="31" t="n"/>
       <c r="AB26" s="33" t="n"/>
       <c r="AC26" s="31" t="n"/>
@@ -7885,12 +7884,12 @@
         </is>
       </c>
       <c r="C27" s="32" t="n"/>
-      <c r="D27" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="E27" s="32" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="F27" s="31" t="n"/>
       <c r="G27" s="31" t="n"/>
       <c r="H27" s="31" t="n"/>
@@ -7907,7 +7906,7 @@
       <c r="S27" s="31" t="n"/>
       <c r="T27" s="32" t="n"/>
       <c r="U27" s="32" t="n"/>
-      <c r="V27" s="30" t="n"/>
+      <c r="V27" s="32" t="n"/>
       <c r="W27" s="31" t="n"/>
       <c r="X27" s="31" t="n"/>
       <c r="Y27" s="31" t="n"/>
@@ -7954,13 +7953,13 @@
       <c r="N28" s="31" t="n"/>
       <c r="O28" s="31" t="n"/>
       <c r="P28" s="31" t="n"/>
-      <c r="Q28" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="Q28" s="31" t="n"/>
       <c r="R28" s="31" t="n"/>
-      <c r="S28" s="33" t="n"/>
+      <c r="S28" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="T28" s="31" t="n"/>
       <c r="U28" s="32" t="n"/>
       <c r="V28" s="31" t="n"/>
@@ -8003,11 +8002,7 @@
       <c r="G29" s="32" t="n"/>
       <c r="H29" s="31" t="n"/>
       <c r="I29" s="31" t="n"/>
-      <c r="J29" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="J29" s="31" t="n"/>
       <c r="K29" s="31" t="n"/>
       <c r="L29" s="31" t="n"/>
       <c r="M29" s="31" t="n"/>
@@ -8028,7 +8023,11 @@
       <c r="AB29" s="31" t="n"/>
       <c r="AC29" s="31" t="n"/>
       <c r="AD29" s="31" t="n"/>
-      <c r="AE29" s="31" t="n"/>
+      <c r="AE29" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AF29" s="31" t="n"/>
       <c r="AG29" s="31" t="n"/>
       <c r="AH29" s="34" t="n"/>
@@ -8071,13 +8070,13 @@
       <c r="S30" s="31" t="n"/>
       <c r="T30" s="31" t="n"/>
       <c r="U30" s="31" t="n"/>
-      <c r="V30" s="30" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="V30" s="30" t="n"/>
       <c r="W30" s="32" t="n"/>
-      <c r="X30" s="31" t="n"/>
+      <c r="X30" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="Y30" s="31" t="n"/>
       <c r="Z30" s="31" t="n"/>
       <c r="AA30" s="31" t="n"/>
@@ -8118,18 +8117,18 @@
       <c r="J31" s="31" t="n"/>
       <c r="K31" s="31" t="n"/>
       <c r="L31" s="31" t="n"/>
-      <c r="M31" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="M31" s="31" t="n"/>
       <c r="N31" s="31" t="n"/>
       <c r="O31" s="31" t="n"/>
       <c r="P31" s="31" t="n"/>
       <c r="Q31" s="31" t="n"/>
       <c r="R31" s="30" t="n"/>
       <c r="S31" s="31" t="n"/>
-      <c r="T31" s="32" t="n"/>
+      <c r="T31" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="U31" s="31" t="n"/>
       <c r="V31" s="31" t="n"/>
       <c r="W31" s="31" t="n"/>
@@ -8188,16 +8187,16 @@
       <c r="Y32" s="32" t="n"/>
       <c r="Z32" s="31" t="n"/>
       <c r="AA32" s="31" t="n"/>
-      <c r="AB32" s="32" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="AB32" s="32" t="n"/>
       <c r="AC32" s="31" t="n"/>
       <c r="AD32" s="31" t="n"/>
       <c r="AE32" s="32" t="n"/>
       <c r="AF32" s="32" t="n"/>
-      <c r="AG32" s="30" t="n"/>
+      <c r="AG32" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AH32" s="34" t="n"/>
       <c r="AI32" s="34">
         <f>COUNTA(C32:AH32)</f>
@@ -8225,11 +8224,7 @@
       <c r="G33" s="33" t="n"/>
       <c r="H33" s="31" t="n"/>
       <c r="I33" s="31" t="n"/>
-      <c r="J33" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="J33" s="31" t="n"/>
       <c r="K33" s="31" t="n"/>
       <c r="L33" s="31" t="n"/>
       <c r="M33" s="31" t="n"/>
@@ -8248,7 +8243,11 @@
       <c r="Z33" s="32" t="n"/>
       <c r="AA33" s="31" t="n"/>
       <c r="AB33" s="30" t="n"/>
-      <c r="AC33" s="32" t="n"/>
+      <c r="AC33" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AD33" s="31" t="n"/>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="31" t="n"/>
@@ -8294,16 +8293,16 @@
       <c r="U34" s="31" t="n"/>
       <c r="V34" s="31" t="n"/>
       <c r="W34" s="31" t="n"/>
-      <c r="X34" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="X34" s="31" t="n"/>
       <c r="Y34" s="32" t="n"/>
       <c r="Z34" s="31" t="n"/>
       <c r="AB34" s="31" t="n"/>
       <c r="AC34" s="31" t="n"/>
-      <c r="AD34" s="31" t="n"/>
+      <c r="AD34" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AE34" s="30" t="n"/>
       <c r="AF34" s="30" t="n"/>
       <c r="AG34" s="31" t="n"/>
@@ -8337,13 +8336,13 @@
       <c r="J35" s="32" t="n"/>
       <c r="K35" s="31" t="n"/>
       <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n"/>
+      <c r="M35" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="N35" s="31" t="n"/>
-      <c r="O35" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="O35" s="31" t="n"/>
       <c r="P35" s="31" t="n"/>
       <c r="Q35" s="31" t="n"/>
       <c r="R35" s="32" t="n"/>
@@ -8402,11 +8401,7 @@
       <c r="T36" s="32" t="n"/>
       <c r="U36" s="31" t="n"/>
       <c r="V36" s="31" t="n"/>
-      <c r="W36" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="W36" s="31" t="n"/>
       <c r="X36" s="31" t="n"/>
       <c r="Y36" s="31" t="n"/>
       <c r="Z36" s="31" t="n"/>
@@ -8415,7 +8410,11 @@
       <c r="AC36" s="31" t="n"/>
       <c r="AD36" s="31" t="n"/>
       <c r="AE36" s="31" t="n"/>
-      <c r="AF36" s="31" t="n"/>
+      <c r="AF36" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AG36" s="32" t="n"/>
       <c r="AH36" s="34" t="n"/>
       <c r="AI36" s="34">
@@ -8437,14 +8436,14 @@
           <t>Anji</t>
         </is>
       </c>
-      <c r="C37" s="31" t="n"/>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="D37" s="30" t="n"/>
       <c r="E37" s="31" t="n"/>
-      <c r="F37" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="F37" s="31" t="n"/>
       <c r="G37" s="31" t="n"/>
       <c r="H37" s="31" t="n"/>
       <c r="I37" s="31" t="n"/>
@@ -8460,11 +8459,7 @@
       <c r="S37" s="30" t="n"/>
       <c r="T37" s="32" t="n"/>
       <c r="U37" s="30" t="n"/>
-      <c r="V37" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="V37" s="31" t="n"/>
       <c r="W37" s="31" t="n"/>
       <c r="X37" s="31" t="n"/>
       <c r="Y37" s="31" t="n"/>
@@ -8507,18 +8502,18 @@
       <c r="K38" s="31" t="n"/>
       <c r="L38" s="31" t="n"/>
       <c r="M38" s="31" t="n"/>
-      <c r="N38" s="30" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="N38" s="30" t="n"/>
       <c r="O38" s="31" t="n"/>
       <c r="P38" s="31" t="n"/>
       <c r="Q38" s="31" t="n"/>
       <c r="R38" s="31" t="n"/>
       <c r="S38" s="30" t="n"/>
       <c r="T38" s="32" t="n"/>
-      <c r="U38" s="30" t="n"/>
+      <c r="U38" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="V38" s="30" t="n"/>
       <c r="W38" s="31" t="n"/>
       <c r="X38" s="31" t="n"/>
@@ -8567,18 +8562,18 @@
       <c r="P39" s="31" t="n"/>
       <c r="Q39" s="31" t="n"/>
       <c r="R39" s="31" t="n"/>
-      <c r="S39" s="31" t="n"/>
+      <c r="S39" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="T39" s="31" t="n"/>
       <c r="U39" s="31" t="n"/>
       <c r="V39" s="31" t="n"/>
       <c r="W39" s="31" t="n"/>
       <c r="X39" s="31" t="n"/>
       <c r="Y39" s="36" t="n"/>
-      <c r="Z39" s="30" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="Z39" s="30" t="n"/>
       <c r="AA39" s="31" t="n"/>
       <c r="AB39" s="32" t="n"/>
       <c r="AC39" s="32" t="n"/>
@@ -8615,11 +8610,7 @@
       <c r="I40" s="32" t="n"/>
       <c r="J40" s="30" t="n"/>
       <c r="K40" s="30" t="n"/>
-      <c r="L40" s="30" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="L40" s="30" t="n"/>
       <c r="M40" s="31" t="n"/>
       <c r="N40" s="30" t="n"/>
       <c r="O40" s="31" t="n"/>
@@ -8636,7 +8627,11 @@
       <c r="Z40" s="30" t="n"/>
       <c r="AA40" s="31" t="n"/>
       <c r="AB40" s="31" t="n"/>
-      <c r="AC40" s="33" t="n"/>
+      <c r="AC40" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AD40" s="31" t="n"/>
       <c r="AE40" s="33" t="n"/>
       <c r="AF40" s="33" t="n"/>
@@ -8671,18 +8666,18 @@
       <c r="J41" s="32" t="n"/>
       <c r="K41" s="32" t="n"/>
       <c r="L41" s="32" t="n"/>
-      <c r="M41" s="33" t="n"/>
+      <c r="M41" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="N41" s="31" t="n"/>
       <c r="O41" s="31" t="n"/>
       <c r="P41" s="31" t="n"/>
       <c r="Q41" s="31" t="n"/>
       <c r="R41" s="30" t="n"/>
       <c r="S41" s="31" t="n"/>
-      <c r="T41" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="T41" s="31" t="n"/>
       <c r="U41" s="31" t="n"/>
       <c r="V41" s="31" t="n"/>
       <c r="W41" s="31" t="n"/>
@@ -8716,8 +8711,12 @@
           <t>Shah</t>
         </is>
       </c>
-      <c r="C42" s="31" t="n"/>
-      <c r="D42" s="31" t="n"/>
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="n"/>
       <c r="E42" s="32" t="n"/>
       <c r="F42" s="31" t="n"/>
       <c r="G42" s="31" t="n"/>
@@ -8742,11 +8741,7 @@
       <c r="Z42" s="32" t="n"/>
       <c r="AA42" s="31" t="n"/>
       <c r="AB42" s="31" t="n"/>
-      <c r="AC42" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="AC42" s="31" t="n"/>
       <c r="AD42" s="32" t="n"/>
       <c r="AE42" s="31" t="n"/>
       <c r="AF42" s="31" t="n"/>
@@ -8774,7 +8769,11 @@
       <c r="C43" s="31" t="n"/>
       <c r="D43" s="32" t="n"/>
       <c r="E43" s="31" t="n"/>
-      <c r="F43" s="32" t="n"/>
+      <c r="F43" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="G43" s="31" t="n"/>
       <c r="H43" s="30" t="n"/>
       <c r="I43" s="30" t="n"/>
@@ -8793,11 +8792,7 @@
       <c r="V43" s="31" t="n"/>
       <c r="W43" s="31" t="n"/>
       <c r="X43" s="31" t="n"/>
-      <c r="Y43" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="Y43" s="31" t="n"/>
       <c r="Z43" s="31" t="n"/>
       <c r="AA43" s="31" t="n"/>
       <c r="AB43" s="31" t="n"/>
@@ -8834,7 +8829,11 @@
       <c r="H44" s="32" t="n"/>
       <c r="I44" s="32" t="n"/>
       <c r="J44" s="32" t="n"/>
-      <c r="K44" s="32" t="n"/>
+      <c r="K44" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="L44" s="32" t="n"/>
       <c r="M44" s="31" t="n"/>
       <c r="N44" s="31" t="n"/>
@@ -8845,11 +8844,7 @@
       <c r="S44" s="31" t="n"/>
       <c r="T44" s="32" t="n"/>
       <c r="U44" s="31" t="n"/>
-      <c r="V44" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="V44" s="31" t="n"/>
       <c r="W44" s="31" t="n"/>
       <c r="X44" s="31" t="n"/>
       <c r="Y44" s="31" t="n"/>
@@ -8893,13 +8888,13 @@
       <c r="K45" s="32" t="n"/>
       <c r="L45" s="31" t="n"/>
       <c r="M45" s="32" t="n"/>
-      <c r="N45" s="31" t="n"/>
+      <c r="N45" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="O45" s="30" t="n"/>
-      <c r="P45" s="30" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="P45" s="30" t="n"/>
       <c r="Q45" s="31" t="n"/>
       <c r="R45" s="31" t="n"/>
       <c r="S45" s="31" t="n"/>
@@ -8952,7 +8947,11 @@
       <c r="N46" s="32" t="n"/>
       <c r="O46" s="30" t="n"/>
       <c r="P46" s="31" t="n"/>
-      <c r="Q46" s="31" t="n"/>
+      <c r="Q46" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="R46" s="31" t="n"/>
       <c r="S46" s="31" t="n"/>
       <c r="T46" s="31" t="n"/>
@@ -8990,14 +8989,14 @@
           <t>Ahmad</t>
         </is>
       </c>
-      <c r="C47" s="32" t="n"/>
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="32" t="n"/>
-      <c r="F47" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="F47" s="31" t="n"/>
       <c r="G47" s="31" t="n"/>
       <c r="H47" s="32" t="n"/>
       <c r="I47" s="32" t="n"/>
@@ -9012,11 +9011,7 @@
       <c r="R47" s="31" t="n"/>
       <c r="S47" s="31" t="n"/>
       <c r="T47" s="31" t="n"/>
-      <c r="U47" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="U47" s="31" t="n"/>
       <c r="V47" s="31" t="n"/>
       <c r="W47" s="31" t="n"/>
       <c r="X47" s="31" t="n"/>
@@ -9055,16 +9050,16 @@
       <c r="E48" s="31" t="n"/>
       <c r="F48" s="32" t="n"/>
       <c r="G48" s="31" t="n"/>
-      <c r="H48" s="40" t="n"/>
+      <c r="H48" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="I48" s="32" t="n"/>
       <c r="J48" s="32" t="n"/>
       <c r="K48" s="32" t="n"/>
       <c r="L48" s="31" t="n"/>
-      <c r="M48" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="M48" s="31" t="n"/>
       <c r="N48" s="31" t="n"/>
       <c r="O48" s="31" t="n"/>
       <c r="P48" s="31" t="n"/>
@@ -9081,11 +9076,7 @@
       <c r="AA48" s="32" t="n"/>
       <c r="AB48" s="30" t="n"/>
       <c r="AC48" s="30" t="n"/>
-      <c r="AD48" s="32" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="AD48" s="32" t="n"/>
       <c r="AE48" s="30" t="n"/>
       <c r="AF48" s="30" t="n"/>
       <c r="AG48" s="31" t="n"/>
@@ -9140,7 +9131,11 @@
       <c r="AD49" s="31" t="n"/>
       <c r="AE49" s="31" t="n"/>
       <c r="AF49" s="31" t="n"/>
-      <c r="AG49" s="31" t="n"/>
+      <c r="AG49" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AH49" s="34" t="n"/>
       <c r="AI49" s="34">
         <f>COUNTA(C49:AH49)</f>
@@ -9169,7 +9164,11 @@
       <c r="G50" s="32" t="n"/>
       <c r="H50" s="31" t="n"/>
       <c r="I50" s="31" t="n"/>
-      <c r="J50" s="31" t="n"/>
+      <c r="J50" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="K50" s="32" t="n"/>
       <c r="L50" s="31" t="n"/>
       <c r="M50" s="31" t="n"/>
@@ -9183,11 +9182,7 @@
       <c r="U50" s="31" t="n"/>
       <c r="V50" s="31" t="n"/>
       <c r="W50" s="31" t="n"/>
-      <c r="X50" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="X50" s="31" t="n"/>
       <c r="Y50" s="31" t="n"/>
       <c r="Z50" s="33" t="n"/>
       <c r="AA50" s="31" t="n"/>
@@ -9227,16 +9222,16 @@
       <c r="I51" s="31" t="n"/>
       <c r="J51" s="31" t="n"/>
       <c r="K51" s="32" t="n"/>
-      <c r="L51" s="31" t="n"/>
+      <c r="L51" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="M51" s="31" t="n"/>
       <c r="N51" s="32" t="n"/>
       <c r="O51" s="31" t="n"/>
       <c r="P51" s="31" t="n"/>
-      <c r="Q51" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="Q51" s="31" t="n"/>
       <c r="R51" s="31" t="n"/>
       <c r="S51" s="31" t="n"/>
       <c r="T51" s="31" t="n"/>
@@ -9285,7 +9280,11 @@
       <c r="K52" s="32" t="n"/>
       <c r="L52" s="31" t="n"/>
       <c r="M52" s="30" t="n"/>
-      <c r="N52" s="32" t="n"/>
+      <c r="N52" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="O52" s="31" t="n"/>
       <c r="P52" s="31" t="n"/>
       <c r="Q52" s="31" t="n"/>
@@ -9300,11 +9299,7 @@
       <c r="Z52" s="31" t="n"/>
       <c r="AA52" s="31" t="n"/>
       <c r="AB52" s="31" t="n"/>
-      <c r="AC52" s="30" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="AC52" s="30" t="n"/>
       <c r="AD52" s="32" t="n"/>
       <c r="AE52" s="31" t="n"/>
       <c r="AF52" s="31" t="n"/>
@@ -9347,15 +9342,15 @@
       <c r="Q53" s="31" t="n"/>
       <c r="R53" s="31" t="n"/>
       <c r="S53" s="31" t="n"/>
-      <c r="T53" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="T53" s="31" t="n"/>
       <c r="U53" s="31" t="n"/>
       <c r="V53" s="31" t="n"/>
       <c r="W53" s="31" t="n"/>
-      <c r="X53" s="31" t="n"/>
+      <c r="X53" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="Y53" s="30" t="n"/>
       <c r="Z53" s="31" t="n"/>
       <c r="AA53" s="32" t="n"/>
@@ -9386,8 +9381,12 @@
         </is>
       </c>
       <c r="C54" s="30" t="n"/>
-      <c r="D54" s="31" t="n"/>
-      <c r="E54" s="30" t="n"/>
+      <c r="D54" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="E54" s="32" t="n"/>
       <c r="F54" s="31" t="n"/>
       <c r="G54" s="32" t="n"/>
       <c r="H54" s="30" t="n"/>
@@ -9451,7 +9450,7 @@
       <c r="N55" s="33" t="n"/>
       <c r="O55" s="31" t="n"/>
       <c r="P55" s="31" t="n"/>
-      <c r="Q55" s="31" t="inlineStr">
+      <c r="Q55" s="32" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
@@ -9521,7 +9520,7 @@
       <c r="AB56" s="31" t="n"/>
       <c r="AC56" s="31" t="n"/>
       <c r="AD56" s="31" t="n"/>
-      <c r="AE56" s="31" t="inlineStr">
+      <c r="AE56" s="32" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
@@ -9568,17 +9567,17 @@
       <c r="S57" s="31" t="n"/>
       <c r="T57" s="31" t="n"/>
       <c r="U57" s="31" t="n"/>
-      <c r="V57" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="V57" s="31" t="n"/>
       <c r="W57" s="31" t="n"/>
       <c r="X57" s="31" t="n"/>
       <c r="Y57" s="32" t="n"/>
       <c r="Z57" s="32" t="n"/>
       <c r="AA57" s="31" t="n"/>
-      <c r="AB57" s="31" t="n"/>
+      <c r="AB57" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AC57" s="31" t="n"/>
       <c r="AD57" s="31" t="n"/>
       <c r="AE57" s="31" t="n"/>
@@ -9626,13 +9625,13 @@
       <c r="V58" s="31" t="n"/>
       <c r="W58" s="31" t="n"/>
       <c r="X58" s="31" t="n"/>
-      <c r="Y58" s="32" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="Y58" s="32" t="n"/>
       <c r="Z58" s="31" t="n"/>
-      <c r="AA58" s="31" t="n"/>
+      <c r="AA58" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AB58" s="31" t="n"/>
       <c r="AC58" s="31" t="n"/>
       <c r="AD58" s="33" t="n"/>
@@ -9669,21 +9668,13 @@
       <c r="J59" s="31" t="n"/>
       <c r="K59" s="31" t="n"/>
       <c r="L59" s="31" t="n"/>
-      <c r="M59" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="M59" s="31" t="n"/>
       <c r="N59" s="31" t="n"/>
       <c r="O59" s="31" t="n"/>
       <c r="P59" s="31" t="n"/>
       <c r="Q59" s="31" t="n"/>
       <c r="R59" s="31" t="n"/>
-      <c r="S59" s="40" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="S59" s="40" t="n"/>
       <c r="T59" s="31" t="n"/>
       <c r="U59" s="31" t="n"/>
       <c r="V59" s="30" t="n"/>
@@ -9692,12 +9683,12 @@
       <c r="Y59" s="32" t="n"/>
       <c r="Z59" s="30" t="n"/>
       <c r="AA59" s="31" t="n"/>
-      <c r="AB59" s="32" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="AC59" s="31" t="n"/>
+      <c r="AB59" s="32" t="n"/>
+      <c r="AC59" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AD59" s="32" t="n"/>
       <c r="AE59" s="32" t="n"/>
       <c r="AF59" s="32" t="n"/>
@@ -9722,11 +9713,7 @@
           <t>Dauson</t>
         </is>
       </c>
-      <c r="C60" s="38" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="C60" s="38" t="n"/>
       <c r="D60" s="33" t="n"/>
       <c r="E60" s="31" t="n"/>
       <c r="F60" s="31" t="n"/>
@@ -9746,15 +9733,15 @@
       <c r="T60" s="31" t="n"/>
       <c r="U60" s="30" t="n"/>
       <c r="V60" s="30" t="n"/>
-      <c r="W60" s="31" t="n"/>
+      <c r="W60" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="X60" s="32" t="n"/>
       <c r="Y60" s="31" t="n"/>
       <c r="Z60" s="30" t="n"/>
-      <c r="AA60" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="AA60" s="31" t="n"/>
       <c r="AB60" s="31" t="n"/>
       <c r="AC60" s="33" t="n"/>
       <c r="AD60" s="31" t="n"/>
@@ -9800,15 +9787,15 @@
       <c r="T61" s="30" t="n"/>
       <c r="U61" s="30" t="n"/>
       <c r="V61" s="30" t="n"/>
-      <c r="W61" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="W61" s="31" t="n"/>
       <c r="X61" s="32" t="n"/>
       <c r="Y61" s="30" t="n"/>
       <c r="Z61" s="32" t="n"/>
-      <c r="AA61" s="32" t="n"/>
+      <c r="AA61" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AB61" s="31" t="n"/>
       <c r="AC61" s="31" t="n"/>
       <c r="AD61" s="31" t="n"/>
@@ -9860,7 +9847,11 @@
       <c r="Y62" s="32" t="n"/>
       <c r="Z62" s="32" t="n"/>
       <c r="AA62" s="31" t="n"/>
-      <c r="AB62" s="31" t="n"/>
+      <c r="AB62" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AC62" s="31" t="n"/>
       <c r="AD62" s="32" t="n"/>
       <c r="AE62" s="31" t="n"/>
@@ -9890,6 +9881,11 @@
       <c r="C63" s="31" t="n"/>
       <c r="D63" s="32" t="n"/>
       <c r="E63" s="31" t="n"/>
+      <c r="F63" s="68" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="G63" s="31" t="n"/>
       <c r="H63" s="32" t="n"/>
       <c r="I63" s="31" t="n"/>
@@ -9947,11 +9943,7 @@
           <t>AU</t>
         </is>
       </c>
-      <c r="H64" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="H64" s="31" t="n"/>
       <c r="I64" s="31" t="n"/>
       <c r="J64" s="32" t="n"/>
       <c r="K64" s="32" t="n"/>
@@ -9966,11 +9958,7 @@
       <c r="T64" s="31" t="n"/>
       <c r="U64" s="31" t="n"/>
       <c r="V64" s="31" t="n"/>
-      <c r="W64" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="W64" s="31" t="n"/>
       <c r="X64" s="31" t="n"/>
       <c r="Y64" s="31" t="n"/>
       <c r="Z64" s="31" t="n"/>
@@ -10014,11 +10002,7 @@
       <c r="L65" s="32" t="n"/>
       <c r="M65" s="32" t="n"/>
       <c r="N65" s="31" t="n"/>
-      <c r="O65" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="O65" s="31" t="n"/>
       <c r="P65" s="31" t="n"/>
       <c r="Q65" s="31" t="n"/>
       <c r="R65" s="31" t="n"/>
@@ -10033,7 +10017,11 @@
       <c r="AA65" s="31" t="n"/>
       <c r="AB65" s="33" t="n"/>
       <c r="AC65" s="33" t="n"/>
-      <c r="AD65" s="31" t="n"/>
+      <c r="AD65" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AE65" s="31" t="n"/>
       <c r="AF65" s="31" t="n"/>
       <c r="AG65" s="31" t="n"/>
@@ -10069,7 +10057,11 @@
       <c r="K66" s="31" t="n"/>
       <c r="L66" s="32" t="n"/>
       <c r="M66" s="32" t="n"/>
-      <c r="N66" s="32" t="n"/>
+      <c r="N66" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="O66" s="31" t="n"/>
       <c r="P66" s="31" t="n"/>
       <c r="Q66" s="31" t="n"/>
@@ -10082,11 +10074,7 @@
       <c r="X66" s="30" t="n"/>
       <c r="Y66" s="31" t="n"/>
       <c r="Z66" s="31" t="n"/>
-      <c r="AA66" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="AA66" s="31" t="n"/>
       <c r="AB66" s="31" t="n"/>
       <c r="AC66" s="31" t="n"/>
       <c r="AD66" s="31" t="n"/>
@@ -10126,7 +10114,11 @@
       <c r="L67" s="31" t="n"/>
       <c r="M67" s="32" t="n"/>
       <c r="N67" s="31" t="n"/>
-      <c r="O67" s="31" t="n"/>
+      <c r="O67" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="P67" s="31" t="n"/>
       <c r="Q67" s="31" t="n"/>
       <c r="R67" s="31" t="n"/>
@@ -10181,13 +10173,13 @@
       <c r="P68" s="32" t="n"/>
       <c r="Q68" s="31" t="n"/>
       <c r="R68" s="31" t="n"/>
-      <c r="S68" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="S68" s="31" t="n"/>
       <c r="T68" s="31" t="n"/>
-      <c r="U68" s="31" t="n"/>
+      <c r="U68" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="V68" s="31" t="n"/>
       <c r="W68" s="31" t="n"/>
       <c r="X68" s="31" t="n"/>
@@ -10221,7 +10213,11 @@
         </is>
       </c>
       <c r="C69" s="31" t="n"/>
-      <c r="D69" s="30" t="n"/>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="E69" s="31" t="n"/>
       <c r="F69" s="31" t="n"/>
       <c r="G69" s="31" t="n"/>
@@ -10286,15 +10282,15 @@
       <c r="O70" s="30" t="n"/>
       <c r="P70" s="32" t="n"/>
       <c r="Q70" s="31" t="n"/>
-      <c r="R70" s="31" t="n"/>
+      <c r="R70" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="S70" s="31" t="n"/>
       <c r="T70" s="31" t="n"/>
       <c r="U70" s="31" t="n"/>
-      <c r="V70" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="V70" s="31" t="n"/>
       <c r="W70" s="31" t="n"/>
       <c r="X70" s="31" t="n"/>
       <c r="Y70" s="31" t="n"/>
@@ -10333,7 +10329,11 @@
       <c r="F71" s="30" t="n"/>
       <c r="G71" s="31" t="n"/>
       <c r="H71" s="31" t="n"/>
-      <c r="I71" s="32" t="n"/>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="J71" s="30" t="n"/>
       <c r="K71" s="30" t="n"/>
       <c r="L71" s="30" t="n"/>
@@ -10379,14 +10379,14 @@
         </is>
       </c>
       <c r="C72" s="31" t="n"/>
-      <c r="D72" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="D72" s="31" t="n"/>
       <c r="E72" s="31" t="n"/>
       <c r="F72" s="30" t="n"/>
-      <c r="G72" s="31" t="n"/>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="H72" s="31" t="n"/>
       <c r="I72" s="30" t="n"/>
       <c r="J72" s="30" t="n"/>
@@ -10398,11 +10398,7 @@
       <c r="P72" s="33" t="n"/>
       <c r="Q72" s="31" t="n"/>
       <c r="R72" s="31" t="n"/>
-      <c r="S72" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="S72" s="31" t="n"/>
       <c r="T72" s="31" t="n"/>
       <c r="U72" s="31" t="n"/>
       <c r="V72" s="31" t="n"/>
@@ -10451,23 +10447,19 @@
       <c r="N73" s="31" t="n"/>
       <c r="O73" s="31" t="n"/>
       <c r="P73" s="31" t="n"/>
-      <c r="Q73" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="Q73" s="31" t="n"/>
       <c r="R73" s="31" t="n"/>
-      <c r="S73" s="31" t="n"/>
+      <c r="S73" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="T73" s="31" t="n"/>
       <c r="U73" s="31" t="n"/>
       <c r="V73" s="32" t="n"/>
       <c r="W73" s="31" t="n"/>
       <c r="X73" s="31" t="n"/>
-      <c r="Y73" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="Y73" s="31" t="n"/>
       <c r="Z73" s="31" t="n"/>
       <c r="AA73" s="31" t="n"/>
       <c r="AB73" s="32" t="n"/>
@@ -10503,11 +10495,7 @@
       <c r="G74" s="31" t="n"/>
       <c r="H74" s="31" t="n"/>
       <c r="I74" s="31" t="n"/>
-      <c r="J74" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="J74" s="31" t="n"/>
       <c r="K74" s="31" t="n"/>
       <c r="L74" s="31" t="n"/>
       <c r="M74" s="31" t="n"/>
@@ -10518,22 +10506,18 @@
       <c r="R74" s="31" t="n"/>
       <c r="S74" s="32" t="n"/>
       <c r="T74" s="31" t="n"/>
-      <c r="U74" s="31" t="n"/>
+      <c r="U74" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="V74" s="31" t="n"/>
       <c r="W74" s="31" t="n"/>
-      <c r="X74" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="X74" s="31" t="n"/>
       <c r="Y74" s="31" t="n"/>
       <c r="Z74" s="31" t="n"/>
       <c r="AA74" s="31" t="n"/>
-      <c r="AB74" s="32" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="AB74" s="32" t="n"/>
       <c r="AD74" s="31" t="n"/>
       <c r="AE74" s="31" t="n"/>
       <c r="AF74" s="31" t="n"/>
@@ -10566,7 +10550,11 @@
       <c r="G75" s="31" t="n"/>
       <c r="H75" s="31" t="n"/>
       <c r="I75" s="31" t="n"/>
-      <c r="J75" s="31" t="n"/>
+      <c r="J75" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="K75" s="31" t="n"/>
       <c r="L75" s="31" t="n"/>
       <c r="M75" s="31" t="n"/>
@@ -10619,13 +10607,13 @@
       <c r="H76" s="31" t="n"/>
       <c r="I76" s="31" t="n"/>
       <c r="J76" s="31" t="n"/>
-      <c r="K76" s="31" t="n"/>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="L76" s="31" t="n"/>
-      <c r="M76" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="M76" s="31" t="n"/>
       <c r="N76" s="31" t="n"/>
       <c r="O76" s="31" t="n"/>
       <c r="P76" s="31" t="n"/>
@@ -10633,11 +10621,7 @@
       <c r="R76" s="30" t="n"/>
       <c r="S76" s="31" t="n"/>
       <c r="T76" s="31" t="n"/>
-      <c r="U76" s="40" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="U76" s="40" t="n"/>
       <c r="V76" s="31" t="n"/>
       <c r="W76" s="31" t="n"/>
       <c r="X76" s="30" t="n"/>
@@ -10693,12 +10677,12 @@
       <c r="V77" s="31" t="n"/>
       <c r="W77" s="30" t="n"/>
       <c r="X77" s="30" t="n"/>
-      <c r="Y77" s="30" t="n"/>
-      <c r="Z77" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="Y77" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Z77" s="31" t="n"/>
       <c r="AA77" s="32" t="n"/>
       <c r="AB77" s="30" t="n"/>
       <c r="AC77" s="31" t="n"/>
@@ -10733,17 +10717,17 @@
       <c r="G78" s="30" t="n"/>
       <c r="H78" s="31" t="n"/>
       <c r="I78" s="31" t="n"/>
-      <c r="J78" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="J78" s="31" t="n"/>
       <c r="K78" s="31" t="n"/>
       <c r="L78" s="31" t="n"/>
       <c r="M78" s="31" t="n"/>
       <c r="N78" s="31" t="n"/>
       <c r="O78" s="31" t="n"/>
-      <c r="P78" s="31" t="n"/>
+      <c r="P78" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="Q78" s="32" t="n"/>
       <c r="R78" s="31" t="n"/>
       <c r="S78" s="31" t="n"/>
@@ -10805,7 +10789,11 @@
       <c r="W79" s="31" t="n"/>
       <c r="X79" s="31" t="n"/>
       <c r="Y79" s="31" t="n"/>
-      <c r="Z79" s="32" t="n"/>
+      <c r="Z79" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AA79" s="31" t="n"/>
       <c r="AB79" s="32" t="n"/>
       <c r="AC79" s="32" t="n"/>
@@ -10845,11 +10833,7 @@
       <c r="L80" s="31" t="n"/>
       <c r="M80" s="31" t="n"/>
       <c r="N80" s="31" t="n"/>
-      <c r="O80" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="O80" s="31" t="n"/>
       <c r="P80" s="31" t="n"/>
       <c r="Q80" s="31" t="n"/>
       <c r="R80" s="32" t="n"/>
@@ -10858,14 +10842,14 @@
       <c r="U80" s="31" t="n"/>
       <c r="V80" s="32" t="n"/>
       <c r="W80" s="31" t="n"/>
-      <c r="X80" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="X80" s="31" t="n"/>
       <c r="Y80" s="31" t="n"/>
       <c r="Z80" s="31" t="n"/>
-      <c r="AA80" s="32" t="n"/>
+      <c r="AA80" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AB80" s="30" t="n"/>
       <c r="AC80" s="31" t="n"/>
       <c r="AD80" s="31" t="n"/>
@@ -10907,30 +10891,22 @@
       <c r="O81" s="31" t="n"/>
       <c r="P81" s="31" t="n"/>
       <c r="Q81" s="31" t="n"/>
-      <c r="R81" s="32" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="R81" s="32" t="n"/>
       <c r="S81" s="31" t="n"/>
       <c r="T81" s="31" t="n"/>
       <c r="U81" s="31" t="n"/>
       <c r="V81" s="31" t="n"/>
-      <c r="W81" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="W81" s="31" t="n"/>
       <c r="X81" s="31" t="n"/>
       <c r="Y81" s="31" t="n"/>
       <c r="Z81" s="31" t="n"/>
-      <c r="AA81" s="32" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="AA81" s="32" t="n"/>
       <c r="AC81" s="31" t="n"/>
-      <c r="AD81" s="31" t="n"/>
+      <c r="AD81" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="AE81" s="31" t="n"/>
       <c r="AF81" s="31" t="n"/>
       <c r="AG81" s="32" t="n"/>
@@ -10963,7 +10939,7 @@
       <c r="I82" s="31" t="n"/>
       <c r="J82" s="31" t="n"/>
       <c r="K82" s="31" t="n"/>
-      <c r="L82" s="40" t="inlineStr">
+      <c r="L82" s="32" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
@@ -11008,7 +10984,11 @@
           <t>Lillian</t>
         </is>
       </c>
-      <c r="C83" s="31" t="n"/>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="D83" s="32" t="n"/>
       <c r="E83" s="31" t="n"/>
       <c r="G83" s="32" t="n"/>
@@ -11062,7 +11042,11 @@
       <c r="C84" s="32" t="n"/>
       <c r="D84" s="32" t="n"/>
       <c r="E84" s="31" t="n"/>
-      <c r="F84" s="31" t="n"/>
+      <c r="F84" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="G84" s="32" t="n"/>
       <c r="H84" s="31" t="n"/>
       <c r="I84" s="31" t="n"/>
@@ -11072,11 +11056,7 @@
       <c r="M84" s="30" t="n"/>
       <c r="N84" s="30" t="n"/>
       <c r="O84" s="30" t="n"/>
-      <c r="P84" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="P84" s="31" t="n"/>
       <c r="Q84" s="32" t="n"/>
       <c r="R84" s="30" t="n"/>
       <c r="S84" s="31" t="n"/>
@@ -11085,11 +11065,7 @@
       <c r="V84" s="31" t="n"/>
       <c r="W84" s="30" t="n"/>
       <c r="X84" s="30" t="n"/>
-      <c r="Y84" s="31" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="Y84" s="31" t="n"/>
       <c r="Z84" s="32" t="n"/>
       <c r="AA84" s="30" t="n"/>
       <c r="AB84" s="31" t="n"/>
@@ -11123,7 +11099,11 @@
       <c r="D85" s="30" t="n"/>
       <c r="E85" s="30" t="n"/>
       <c r="F85" s="30" t="n"/>
-      <c r="G85" s="32" t="n"/>
+      <c r="G85" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="H85" s="30" t="n"/>
       <c r="I85" s="32" t="n"/>
       <c r="J85" s="30" t="n"/>
@@ -11181,7 +11161,11 @@
       <c r="K86" s="31" t="n"/>
       <c r="L86" s="31" t="n"/>
       <c r="M86" s="31" t="n"/>
-      <c r="N86" s="31" t="n"/>
+      <c r="N86" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="O86" s="31" t="n"/>
       <c r="P86" s="31" t="n"/>
       <c r="Q86" s="32" t="n"/>
@@ -11239,7 +11223,11 @@
       <c r="R87" s="31" t="n"/>
       <c r="S87" s="31" t="n"/>
       <c r="U87" s="31" t="n"/>
-      <c r="V87" s="32" t="n"/>
+      <c r="V87" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="W87" s="30" t="n"/>
       <c r="X87" s="31" t="n"/>
       <c r="Y87" s="31" t="n"/>
@@ -11278,7 +11266,11 @@
       <c r="F88" s="30" t="n"/>
       <c r="G88" s="30" t="n"/>
       <c r="H88" s="30" t="n"/>
-      <c r="I88" s="32" t="n"/>
+      <c r="I88" s="32" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
       <c r="J88" s="32" t="n"/>
       <c r="K88" s="30" t="n"/>
       <c r="L88" s="30" t="n"/>
@@ -11432,11 +11424,12 @@
         <f>COUNTA(AE5:AE88)</f>
         <v/>
       </c>
-      <c r="AF89" s="46" t="n">
-        <v>0</v>
+      <c r="AF89" s="46">
+        <f>COUNTA(AF5:AF88)</f>
+        <v/>
       </c>
       <c r="AG89" s="46">
-        <f>AG93</f>
+        <f>COUNTA(AG5:AG88)</f>
         <v/>
       </c>
       <c r="AH89" s="46">
